--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/04_İç Tetkik ve İyileştirme/EKG-KLT-LST-08_nitelikli_ic_tetkikci_listesi_ve_yillik_plan.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/04_İç Tetkik ve İyileştirme/EKG-KLT-LST-08_nitelikli_ic_tetkikci_listesi_ve_yillik_plan.xlsx
@@ -751,7 +751,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-08&amp;C&amp;"Arial,Regular"&amp;11Nitelikli İç Tetkikçi Listesi ve Yıllık Plan</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Tetkikçi faaliyeti gerçek tarih ve rapor kanıtına bağlandı; program çakışması önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -883,7 +884,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-08&amp;C&amp;"Arial,Regular"&amp;11Nitelikli İç Tetkikçi Listesi ve Yıllık Plan</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Tetkikçi faaliyeti gerçek tarih ve rapor kanıtına bağlandı; program çakışması önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>